--- a/SAM_Opportunities_Report_20260612_PM.xlsx
+++ b/SAM_Opportunities_Report_20260612_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -855,7 +855,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>139</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F26" s="26" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F31" s="26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1243,14 +1243,14 @@
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>→  57 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
+          <t>→  56 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>→  10 SDVOSB Solicitation(s) identified — strategic priority for SYTE Corp.</t>
+          <t>→  11 SDVOSB Solicitation(s) identified — strategic priority for SYTE Corp.</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N94"/>
+  <dimension ref="B2:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1336,7 +1336,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  89 records  ·  As of June 12, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  91 records  ·  As of June 12, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -4565,22 +4565,22 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>W9124D26QA266</t>
+          <t>1605AE-26-Q-00005</t>
         </is>
       </c>
       <c r="D53" s="36" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>1605AE-26-Q-00005</t>
+          <t>FA469026Q0030</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+          <t>Video Intercom System</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Ellsworth AFB, South Dakota</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -4692,49 +4692,49 @@
       </c>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>FA469026Q0030</t>
-        </is>
-      </c>
-      <c r="D55" s="36" t="inlineStr">
-        <is>
-          <t>Video Intercom System</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>Ellsworth AFB, South Dakota</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>12d</t>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>36C78626R0059_1</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="inlineStr">
+        <is>
+          <t>Project # 962CM3003 | Cemetery Improvement Project at Mare  Island Naval Cemetery</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Vallejo, California</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="I55" s="23" t="inlineStr">
+        <is>
+          <t>Jun 26, 2026</t>
+        </is>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>13d</t>
         </is>
       </c>
       <c r="K55" s="18" t="inlineStr">
@@ -4742,64 +4742,64 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M55" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N55" s="38" t="inlineStr">
+      <c r="L55" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="B56" s="39" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
-        <is>
-          <t>36C78626R0059_1</t>
-        </is>
-      </c>
-      <c r="D56" s="28" t="inlineStr">
-        <is>
-          <t>Project # 962CM3003 | Cemetery Improvement Project at Mare  Island Naval Cemetery</t>
-        </is>
-      </c>
-      <c r="E56" s="23" t="inlineStr">
-        <is>
-          <t>Vallejo, California</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>140P5426R0010</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G56" s="40" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H56" s="23" t="inlineStr">
-        <is>
-          <t>$7.5M</t>
-        </is>
-      </c>
-      <c r="I56" s="23" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>Jun 26, 2026</t>
         </is>
       </c>
-      <c r="J56" s="23" t="inlineStr">
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t>13d</t>
         </is>
@@ -4809,17 +4809,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L56" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N56" s="42" t="inlineStr">
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0010</t>
+          <t>140R4026R0006</t>
         </is>
       </c>
       <c r="D57" s="36" t="inlineStr">
         <is>
-          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
+          <t>N--GC26 SCADA UPS REPLACEMENT</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G57" s="20" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>140R4026R0006</t>
+          <t>89503426BWA000066</t>
         </is>
       </c>
       <c r="D58" s="33" t="inlineStr">
         <is>
-          <t>N--GC26 SCADA UPS REPLACEMENT</t>
+          <t>Carpenter Substation Stage 03 South Dakota</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -4967,22 +4967,22 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000066</t>
+          <t>140P6026Q0025</t>
         </is>
       </c>
       <c r="D59" s="36" t="inlineStr">
         <is>
-          <t>Carpenter Substation Stage 03 South Dakota</t>
+          <t>FOSM - Replace Backflow Prevention Assemblies</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Smith, Arkansas</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>140P6026Q0025</t>
+          <t>FA441826Q0067</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+          <t>841st Network Cabling Installation</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>Fort Smith, Arkansas</t>
+          <t>North Charleston, South Carolina</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>FA441826Q0067</t>
+          <t>140R2026R0007</t>
         </is>
       </c>
       <c r="D61" s="36" t="inlineStr">
         <is>
-          <t>841st Network Cabling Installation</t>
+          <t>Z--CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>North Charleston, South Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 27, 2026</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="K61" s="18" t="inlineStr">
@@ -5161,114 +5161,114 @@
       </c>
     </row>
     <row r="62" ht="32" customHeight="1">
-      <c r="B62" s="17" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>140R2026R0007</t>
-        </is>
-      </c>
-      <c r="D62" s="33" t="inlineStr">
-        <is>
-          <t>Z--CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>W912QR26RA033</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="inlineStr">
+        <is>
+          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>Anniston, Alabama</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="23" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>16d</t>
+        </is>
+      </c>
+      <c r="K62" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L62" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>89503426BWA000067</t>
+        </is>
+      </c>
+      <c r="D63" s="36" t="inlineStr">
+        <is>
+          <t>Denison Substation Stage 10, Iowa</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H62" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27, 2026</t>
-        </is>
-      </c>
-      <c r="J62" s="17" t="inlineStr">
-        <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="K62" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
-        </is>
-      </c>
-      <c r="L62" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="B63" s="39" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>W912QR26RA033</t>
-        </is>
-      </c>
-      <c r="D63" s="28" t="inlineStr">
-        <is>
-          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
-        </is>
-      </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>Anniston, Alabama</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="G63" s="40" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H63" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="23" t="inlineStr">
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="J63" s="23" t="inlineStr">
+      <c r="J63" s="20" t="inlineStr">
         <is>
           <t>16d</t>
         </is>
@@ -5278,17 +5278,17 @@
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L63" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="42" t="inlineStr">
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5302,22 +5302,22 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>89503426BWA000067</t>
+          <t>140P6026B0005</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>Denison Substation Stage 10, Iowa</t>
+          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Grand Portage, Minnesota</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0005</t>
+          <t>W912PM26BA001</t>
         </is>
       </c>
       <c r="D65" s="36" t="inlineStr">
         <is>
-          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
+          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>Grand Portage, Minnesota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>W912PM26BA001</t>
+          <t>W9123826RA016</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -5496,134 +5496,134 @@
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="39" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="C67" s="20" t="inlineStr">
-        <is>
-          <t>W9123826RA016</t>
-        </is>
-      </c>
-      <c r="D67" s="36" t="inlineStr">
-        <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
-        </is>
-      </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>36C10F26B0001</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="inlineStr">
+        <is>
+          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="G67" s="40" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="I67" s="23" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="K67" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L67" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>W911WN26BA014</t>
+        </is>
+      </c>
+      <c r="D68" s="33" t="inlineStr">
+        <is>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="G67" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H67" s="20" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="I67" s="20" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="J67" s="20" t="inlineStr">
-        <is>
-          <t>16d</t>
-        </is>
-      </c>
-      <c r="K67" s="43" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="J68" s="17" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="K68" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L67" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="B68" s="39" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>36C10F26B0001</t>
-        </is>
-      </c>
-      <c r="D68" s="28" t="inlineStr">
-        <is>
-          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
-        </is>
-      </c>
-      <c r="E68" s="23" t="inlineStr">
-        <is>
-          <t>San Antonio, Texas</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G68" s="40" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H68" s="23" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="I68" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="J68" s="23" t="inlineStr">
-        <is>
-          <t>17d</t>
-        </is>
-      </c>
-      <c r="K68" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L68" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="42" t="inlineStr">
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5637,22 +5637,22 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="D69" s="36" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
@@ -5704,17 +5704,17 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>140FC226R0002</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>MN VLY NWR-HOGBACK LEVEE-FLOOD REPAIR</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>140FC226R0002</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="D71" s="36" t="inlineStr">
         <is>
-          <t>MN VLY NWR-HOGBACK LEVEE-FLOOD REPAIR</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W912ES26QA067</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -5898,47 +5898,47 @@
       </c>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="B73" s="20" t="inlineStr">
+      <c r="B73" s="39" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="C73" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26QA067</t>
-        </is>
-      </c>
-      <c r="D73" s="36" t="inlineStr">
-        <is>
-          <t>Fiber Optic Cable Replacement</t>
-        </is>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>36C25226Q0526</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="inlineStr">
+        <is>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="G73" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="G73" s="40" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="J73" s="20" t="inlineStr">
+      <c r="J73" s="23" t="inlineStr">
         <is>
           <t>17d</t>
         </is>
@@ -5948,17 +5948,17 @@
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L73" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="38" t="inlineStr">
+      <c r="L73" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -7245,134 +7245,268 @@
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
+          <t>W9124D26QA266</t>
+        </is>
+      </c>
+      <c r="D93" s="36" t="inlineStr">
+        <is>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>North Chicago, Illinois</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="J93" s="20" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K93" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
           <t>140L3626Q0032</t>
         </is>
       </c>
-      <c r="D93" s="36" t="inlineStr">
+      <c r="D94" s="33" t="inlineStr">
         <is>
           <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
-      <c r="E93" s="20" t="inlineStr">
+      <c r="E94" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
+      <c r="F94" s="17" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="G93" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="20" t="inlineStr">
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
         <is>
           <t>Jul 15, 2026</t>
         </is>
       </c>
-      <c r="J93" s="20" t="inlineStr">
+      <c r="J94" s="17" t="inlineStr">
         <is>
           <t>32d</t>
         </is>
       </c>
-      <c r="K93" s="44" t="inlineStr">
+      <c r="K94" s="44" t="inlineStr">
         <is>
           <t>⬜ Watch</t>
         </is>
       </c>
-      <c r="L93" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M93" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N93" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="B94" s="39" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="C94" s="23" t="inlineStr">
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M94" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="inlineStr">
+        <is>
+          <t>W9127826RA059</t>
+        </is>
+      </c>
+      <c r="D95" s="36" t="inlineStr">
+        <is>
+          <t>Water Tank Storage</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="20" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="J95" s="20" t="inlineStr">
+        <is>
+          <t>33d</t>
+        </is>
+      </c>
+      <c r="K95" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M95" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="B96" s="39" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C96" s="23" t="inlineStr">
         <is>
           <t>36C25626R0015</t>
         </is>
       </c>
-      <c r="D94" s="28" t="inlineStr">
+      <c r="D96" s="28" t="inlineStr">
         <is>
           <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
         </is>
       </c>
-      <c r="E94" s="23" t="inlineStr">
+      <c r="E96" s="23" t="inlineStr">
         <is>
           <t>Fayetteville, Arkansas</t>
         </is>
       </c>
-      <c r="F94" s="23" t="inlineStr">
+      <c r="F96" s="23" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="G94" s="40" t="inlineStr">
+      <c r="G96" s="40" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="H94" s="23" t="inlineStr">
+      <c r="H96" s="23" t="inlineStr">
         <is>
           <t>$15.0M</t>
         </is>
       </c>
-      <c r="I94" s="23" t="inlineStr">
+      <c r="I96" s="23" t="inlineStr">
         <is>
           <t>Jul 23, 2026</t>
         </is>
       </c>
-      <c r="J94" s="23" t="inlineStr">
+      <c r="J96" s="23" t="inlineStr">
         <is>
           <t>40d</t>
         </is>
       </c>
-      <c r="K94" s="44" t="inlineStr">
+      <c r="K96" s="44" t="inlineStr">
         <is>
           <t>⬜ Watch</t>
         </is>
       </c>
-      <c r="L94" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M94" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N94" s="42" t="inlineStr">
+      <c r="L96" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N96" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:N94"/>
+  <autoFilter ref="B5:N96"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7467,6 +7601,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10077,7 +10213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K142"/>
+  <dimension ref="B2:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10105,7 +10241,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Complete data  ·  137 records  ·  June 12, 2026</t>
+          <t>Complete data  ·  139 records  ·  June 12, 2026</t>
         </is>
       </c>
     </row>
@@ -12609,22 +12745,22 @@
     <row r="53" ht="28" customHeight="1">
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>W9124D26QA266</t>
+          <t>1605AE-26-Q-00005</t>
         </is>
       </c>
       <c r="C53" s="36" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
@@ -12661,22 +12797,22 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>1605AE-26-Q-00005</t>
+          <t>FA469026Q0030</t>
         </is>
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+          <t>Video Intercom System</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Ellsworth AFB, South Dakota</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -12711,104 +12847,104 @@
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>FA469026Q0030</t>
-        </is>
-      </c>
-      <c r="C55" s="36" t="inlineStr">
-        <is>
-          <t>Video Intercom System</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>Ellsworth AFB, South Dakota</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
-        <is>
-          <t>12d</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>36C78626R0059_1</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>Project # 962CM3003 | Cemetery Improvement Project at Mare  Island Naval Cemetery</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Vallejo, California</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>Jun 26, 2026</t>
+        </is>
+      </c>
+      <c r="I55" s="23" t="inlineStr">
+        <is>
+          <t>13d</t>
+        </is>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K55" s="38" t="inlineStr">
+      <c r="K55" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="B56" s="23" t="inlineStr">
-        <is>
-          <t>36C78626R0059_1</t>
-        </is>
-      </c>
-      <c r="C56" s="28" t="inlineStr">
-        <is>
-          <t>Project # 962CM3003 | Cemetery Improvement Project at Mare  Island Naval Cemetery</t>
-        </is>
-      </c>
-      <c r="D56" s="23" t="inlineStr">
-        <is>
-          <t>Vallejo, California</t>
-        </is>
-      </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>140P5426R0010</t>
+        </is>
+      </c>
+      <c r="C56" s="33" t="inlineStr">
+        <is>
+          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr">
-        <is>
-          <t>$7.5M</t>
-        </is>
-      </c>
-      <c r="H56" s="23" t="inlineStr">
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
         <is>
           <t>Jun 26, 2026</t>
         </is>
       </c>
-      <c r="I56" s="23" t="inlineStr">
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>13d</t>
         </is>
       </c>
-      <c r="J56" s="23" t="inlineStr">
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K56" s="42" t="inlineStr">
+      <c r="K56" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12817,12 +12953,12 @@
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0010</t>
+          <t>140R4026R0006</t>
         </is>
       </c>
       <c r="C57" s="36" t="inlineStr">
         <is>
-          <t>Y--FOMA REPLACE NATURE TRAIL BOARDWALK RS</t>
+          <t>N--GC26 SCADA UPS REPLACEMENT</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -12832,7 +12968,7 @@
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
@@ -12869,12 +13005,12 @@
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>140R4026R0006</t>
+          <t>89503426BWA000066</t>
         </is>
       </c>
       <c r="C58" s="33" t="inlineStr">
         <is>
-          <t>N--GC26 SCADA UPS REPLACEMENT</t>
+          <t>Carpenter Substation Stage 03 South Dakota</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -12884,7 +13020,7 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
@@ -12921,22 +13057,22 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000066</t>
+          <t>140P6026Q0025</t>
         </is>
       </c>
       <c r="C59" s="36" t="inlineStr">
         <is>
-          <t>Carpenter Substation Stage 03 South Dakota</t>
+          <t>FOSM - Replace Backflow Prevention Assemblies</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Smith, Arkansas</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -12973,22 +13109,22 @@
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>140P6026Q0025</t>
+          <t>FA441826Q0067</t>
         </is>
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>FOSM - Replace Backflow Prevention Assemblies</t>
+          <t>841st Network Cabling Installation</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Fort Smith, Arkansas</t>
+          <t>North Charleston, South Carolina</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -13025,17 +13161,17 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>FA441826Q0067</t>
+          <t>140R2026R0007</t>
         </is>
       </c>
       <c r="C61" s="36" t="inlineStr">
         <is>
-          <t>841st Network Cabling Installation</t>
+          <t>Z--CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>North Charleston, South Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -13055,12 +13191,12 @@
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jun 27, 2026</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
@@ -13075,104 +13211,104 @@
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>140R2026R0007</t>
-        </is>
-      </c>
-      <c r="C62" s="33" t="inlineStr">
-        <is>
-          <t>Z--CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>W912QR26RA033</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
+        <is>
+          <t>Anniston, Alabama</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="I62" s="23" t="inlineStr">
+        <is>
+          <t>16d</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K62" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>89503426BWA000067</t>
+        </is>
+      </c>
+      <c r="C63" s="36" t="inlineStr">
+        <is>
+          <t>Denison Substation Stage 10, Iowa</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="17" t="inlineStr">
-        <is>
-          <t>Jun 27, 2026</t>
-        </is>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="J62" s="17" t="inlineStr">
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>16d</t>
+        </is>
+      </c>
+      <c r="J63" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K62" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>W912QR26RA033</t>
-        </is>
-      </c>
-      <c r="C63" s="28" t="inlineStr">
-        <is>
-          <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
-        </is>
-      </c>
-      <c r="D63" s="23" t="inlineStr">
-        <is>
-          <t>Anniston, Alabama</t>
-        </is>
-      </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="23" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="I63" s="23" t="inlineStr">
-        <is>
-          <t>16d</t>
-        </is>
-      </c>
-      <c r="J63" s="23" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K63" s="42" t="inlineStr">
+      <c r="K63" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13181,22 +13317,22 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>89503426BWA000067</t>
+          <t>140P6026B0005</t>
         </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>Denison Substation Stage 10, Iowa</t>
+          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Grand Portage, Minnesota</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
@@ -13233,22 +13369,22 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0005</t>
+          <t>W912PM26BA001</t>
         </is>
       </c>
       <c r="C65" s="36" t="inlineStr">
         <is>
-          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
+          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>Grand Portage, Minnesota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
@@ -13285,12 +13421,12 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>W912PM26BA001</t>
+          <t>W9123826RA016</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -13300,7 +13436,7 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
@@ -13310,7 +13446,7 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
@@ -13335,104 +13471,104 @@
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="20" t="inlineStr">
-        <is>
-          <t>W9123826RA016</t>
-        </is>
-      </c>
-      <c r="C67" s="36" t="inlineStr">
-        <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
-        </is>
-      </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>36C10F26B0001</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I67" s="23" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K67" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>W911WN26BA014</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="inlineStr">
+        <is>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G67" s="20" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="H67" s="20" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="I67" s="20" t="inlineStr">
-        <is>
-          <t>16d</t>
-        </is>
-      </c>
-      <c r="J67" s="20" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="J68" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K67" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>36C10F26B0001</t>
-        </is>
-      </c>
-      <c r="C68" s="28" t="inlineStr">
-        <is>
-          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
-        </is>
-      </c>
-      <c r="D68" s="23" t="inlineStr">
-        <is>
-          <t>San Antonio, Texas</t>
-        </is>
-      </c>
-      <c r="E68" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="H68" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I68" s="23" t="inlineStr">
-        <is>
-          <t>17d</t>
-        </is>
-      </c>
-      <c r="J68" s="23" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K68" s="42" t="inlineStr">
+      <c r="K68" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13441,22 +13577,22 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="C69" s="36" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -13466,7 +13602,7 @@
       </c>
       <c r="G69" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H69" s="20" t="inlineStr">
@@ -13493,17 +13629,17 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>140FC226R0002</t>
         </is>
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>MN VLY NWR-HOGBACK LEVEE-FLOOD REPAIR</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -13545,22 +13681,22 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>140FC226R0002</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="C71" s="36" t="inlineStr">
         <is>
-          <t>MN VLY NWR-HOGBACK LEVEE-FLOOD REPAIR</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -13597,17 +13733,17 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W912ES26QA067</t>
         </is>
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -13647,52 +13783,52 @@
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
-      <c r="B73" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26QA067</t>
-        </is>
-      </c>
-      <c r="C73" s="36" t="inlineStr">
-        <is>
-          <t>Fiber Optic Cable Replacement</t>
-        </is>
-      </c>
-      <c r="D73" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>36C25226Q0526</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G73" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="I73" s="23" t="inlineStr">
         <is>
           <t>17d</t>
         </is>
       </c>
-      <c r="J73" s="20" t="inlineStr">
+      <c r="J73" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K73" s="38" t="inlineStr">
+      <c r="K73" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14689,258 +14825,258 @@
     <row r="93" ht="28" customHeight="1">
       <c r="B93" s="20" t="inlineStr">
         <is>
+          <t>W9124D26QA266</t>
+        </is>
+      </c>
+      <c r="C93" s="36" t="inlineStr">
+        <is>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>North Chicago, Illinois</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="J93" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K93" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28" customHeight="1">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
           <t>140L3626Q0032</t>
         </is>
       </c>
-      <c r="C93" s="36" t="inlineStr">
+      <c r="C94" s="33" t="inlineStr">
         <is>
           <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
-      <c r="D93" s="20" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E93" s="20" t="inlineStr">
+      <c r="E94" s="17" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G93" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="inlineStr">
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
         <is>
           <t>Jul 15, 2026</t>
         </is>
       </c>
-      <c r="I93" s="20" t="inlineStr">
+      <c r="I94" s="17" t="inlineStr">
         <is>
           <t>32d</t>
         </is>
       </c>
-      <c r="J93" s="20" t="inlineStr">
+      <c r="J94" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K93" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="28" customHeight="1">
-      <c r="B94" s="23" t="inlineStr">
+      <c r="K94" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>W9127826RA059</t>
+        </is>
+      </c>
+      <c r="C95" s="36" t="inlineStr">
+        <is>
+          <t>Water Tank Storage</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="I95" s="20" t="inlineStr">
+        <is>
+          <t>33d</t>
+        </is>
+      </c>
+      <c r="J95" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K95" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="B96" s="23" t="inlineStr">
         <is>
           <t>36C25626R0015</t>
         </is>
       </c>
-      <c r="C94" s="28" t="inlineStr">
+      <c r="C96" s="28" t="inlineStr">
         <is>
           <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
         </is>
       </c>
-      <c r="D94" s="23" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Fayetteville, Arkansas</t>
         </is>
       </c>
-      <c r="E94" s="23" t="inlineStr">
+      <c r="E96" s="23" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F94" s="23" t="inlineStr">
+      <c r="F96" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G94" s="23" t="inlineStr">
+      <c r="G96" s="23" t="inlineStr">
         <is>
           <t>$15.0M</t>
         </is>
       </c>
-      <c r="H94" s="23" t="inlineStr">
+      <c r="H96" s="23" t="inlineStr">
         <is>
           <t>Jul 23, 2026</t>
         </is>
       </c>
-      <c r="I94" s="23" t="inlineStr">
+      <c r="I96" s="23" t="inlineStr">
         <is>
           <t>40d</t>
         </is>
       </c>
-      <c r="J94" s="23" t="inlineStr">
+      <c r="J96" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K94" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="B95" s="23" t="inlineStr">
+      <c r="K96" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="B97" s="23" t="inlineStr">
         <is>
           <t>36C24826R0107</t>
         </is>
       </c>
-      <c r="C95" s="28" t="inlineStr">
+      <c r="C97" s="28" t="inlineStr">
         <is>
           <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
         </is>
       </c>
-      <c r="D95" s="23" t="inlineStr">
+      <c r="D97" s="23" t="inlineStr">
         <is>
           <t>Orlando, Florida</t>
         </is>
       </c>
-      <c r="E95" s="23" t="inlineStr">
+      <c r="E97" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F95" s="23" t="inlineStr">
+      <c r="F97" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H95" s="23" t="inlineStr">
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="23" t="inlineStr">
         <is>
           <t>Jun 15, 2026</t>
         </is>
       </c>
-      <c r="I95" s="23" t="inlineStr">
+      <c r="I97" s="23" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="J95" s="23" t="inlineStr">
+      <c r="J97" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K95" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>W912HN26BA008</t>
-        </is>
-      </c>
-      <c r="C96" s="33" t="inlineStr">
-        <is>
-          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
-        </is>
-      </c>
-      <c r="D96" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E96" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F96" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G96" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" s="17" t="inlineStr">
-        <is>
-          <t>Jun 15, 2026</t>
-        </is>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="J96" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K96" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="B97" s="20" t="inlineStr">
-        <is>
-          <t>W912BU26BA026</t>
-        </is>
-      </c>
-      <c r="C97" s="36" t="inlineStr">
-        <is>
-          <t>Absecon Island Outfalls Repair</t>
-        </is>
-      </c>
-      <c r="D97" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E97" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F97" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G97" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="20" t="inlineStr">
-        <is>
-          <t>Jun 16, 2026</t>
-        </is>
-      </c>
-      <c r="I97" s="20" t="inlineStr">
-        <is>
-          <t>3d</t>
-        </is>
-      </c>
-      <c r="J97" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K97" s="38" t="inlineStr">
+      <c r="K97" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14949,258 +15085,258 @@
     <row r="98" ht="28" customHeight="1">
       <c r="B98" s="17" t="inlineStr">
         <is>
+          <t>W912HN26BA008</t>
+        </is>
+      </c>
+      <c r="C98" s="33" t="inlineStr">
+        <is>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>Jun 15, 2026</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="J98" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K98" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>W912BU26BA026</t>
+        </is>
+      </c>
+      <c r="C99" s="36" t="inlineStr">
+        <is>
+          <t>Absecon Island Outfalls Repair</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F99" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G99" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H99" s="20" t="inlineStr">
+        <is>
+          <t>Jun 16, 2026</t>
+        </is>
+      </c>
+      <c r="I99" s="20" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
+      <c r="J99" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K99" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="B100" s="17" t="inlineStr">
+        <is>
           <t>FA301626FB0001</t>
         </is>
       </c>
-      <c r="C98" s="33" t="inlineStr">
+      <c r="C100" s="33" t="inlineStr">
         <is>
           <t>Repair Carswell Ave.</t>
         </is>
       </c>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="D100" s="17" t="inlineStr">
         <is>
           <t>DWG, Texas</t>
         </is>
       </c>
-      <c r="E98" s="17" t="inlineStr">
+      <c r="E100" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F98" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G98" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H98" s="17" t="inlineStr">
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
         <is>
           <t>Jun 17, 2026</t>
         </is>
       </c>
-      <c r="I98" s="17" t="inlineStr">
+      <c r="I100" s="17" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="J98" s="17" t="inlineStr">
+      <c r="J100" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K98" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="B99" s="23" t="inlineStr">
+      <c r="K100" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="B101" s="23" t="inlineStr">
         <is>
           <t>36C25026B0050</t>
         </is>
       </c>
-      <c r="C99" s="28" t="inlineStr">
+      <c r="C101" s="28" t="inlineStr">
         <is>
           <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
         </is>
       </c>
-      <c r="D99" s="23" t="inlineStr">
+      <c r="D101" s="23" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E99" s="23" t="inlineStr">
+      <c r="E101" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F101" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G99" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="23" t="inlineStr">
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H101" s="23" t="inlineStr">
         <is>
           <t>Jun 17, 2026</t>
         </is>
       </c>
-      <c r="I99" s="23" t="inlineStr">
+      <c r="I101" s="23" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="J99" s="23" t="inlineStr">
+      <c r="J101" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K99" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="B100" s="23" t="inlineStr">
+      <c r="K101" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="B102" s="23" t="inlineStr">
         <is>
           <t>36C25026B0045</t>
         </is>
       </c>
-      <c r="C100" s="28" t="inlineStr">
+      <c r="C102" s="28" t="inlineStr">
         <is>
           <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
         </is>
       </c>
-      <c r="D100" s="23" t="inlineStr">
+      <c r="D102" s="23" t="inlineStr">
         <is>
           <t>Dayton, Ohio</t>
         </is>
       </c>
-      <c r="E100" s="23" t="inlineStr">
+      <c r="E102" s="23" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F100" s="23" t="inlineStr">
+      <c r="F102" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G100" s="23" t="inlineStr">
+      <c r="G102" s="23" t="inlineStr">
         <is>
           <t>$750K</t>
         </is>
       </c>
-      <c r="H100" s="23" t="inlineStr">
+      <c r="H102" s="23" t="inlineStr">
         <is>
           <t>Jun 18, 2026</t>
         </is>
       </c>
-      <c r="I100" s="23" t="inlineStr">
+      <c r="I102" s="23" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="J100" s="23" t="inlineStr">
+      <c r="J102" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K100" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="B101" s="20" t="inlineStr">
-        <is>
-          <t>W911WN26RA011</t>
-        </is>
-      </c>
-      <c r="C101" s="36" t="inlineStr">
-        <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
-        </is>
-      </c>
-      <c r="D101" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E101" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F101" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G101" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="20" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I101" s="20" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
-      <c r="J101" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K101" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>140P6026Q0052</t>
-        </is>
-      </c>
-      <c r="C102" s="33" t="inlineStr">
-        <is>
-          <t>Z--WACO Emergency Generator</t>
-        </is>
-      </c>
-      <c r="D102" s="17" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E102" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F102" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G102" s="17" t="inlineStr">
-        <is>
-          <t>$62K</t>
-        </is>
-      </c>
-      <c r="H102" s="17" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
-      <c r="J102" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K102" s="35" t="inlineStr">
+      <c r="K102" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15209,12 +15345,12 @@
     <row r="103" ht="28" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>36C25226Q0426</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C103" s="36" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -15224,7 +15360,7 @@
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15239,12 +15375,12 @@
       </c>
       <c r="H103" s="20" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
@@ -15261,22 +15397,22 @@
     <row r="104" ht="28" customHeight="1">
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>36C24526Q0576</t>
+          <t>140P6026Q0052</t>
         </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
@@ -15286,17 +15422,17 @@
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J104" s="17" t="inlineStr">
@@ -15313,22 +15449,22 @@
     <row r="105" ht="28" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>FDA-PRESOL-132892</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C105" s="36" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -15338,7 +15474,7 @@
       </c>
       <c r="G105" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H105" s="20" t="inlineStr">
@@ -15365,22 +15501,22 @@
     <row r="106" ht="28" customHeight="1">
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -15395,12 +15531,12 @@
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J106" s="17" t="inlineStr">
@@ -15417,22 +15553,22 @@
     <row r="107" ht="28" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>FDA-PRESOL-132892</t>
         </is>
       </c>
       <c r="C107" s="36" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -15442,17 +15578,17 @@
       </c>
       <c r="G107" s="20" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
@@ -15469,17 +15605,17 @@
     <row r="108" ht="28" customHeight="1">
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>GROUP1-24-R-W001</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
@@ -15494,17 +15630,17 @@
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>$17.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="J108" s="17" t="inlineStr">
@@ -15519,52 +15655,52 @@
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
-      <c r="B109" s="23" t="inlineStr">
-        <is>
-          <t>36C26126R0050</t>
-        </is>
-      </c>
-      <c r="C109" s="28" t="inlineStr">
-        <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
-        </is>
-      </c>
-      <c r="D109" s="23" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="E109" s="23" t="inlineStr">
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>W50S7X-26-B-A003</t>
+        </is>
+      </c>
+      <c r="C109" s="36" t="inlineStr">
+        <is>
+          <t>B16 PLC Replacement</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E109" s="20" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F109" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr">
-        <is>
-          <t>$5.0M</t>
-        </is>
-      </c>
-      <c r="H109" s="23" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I109" s="23" t="inlineStr">
-        <is>
-          <t>11d</t>
-        </is>
-      </c>
-      <c r="J109" s="23" t="inlineStr">
+      <c r="F109" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G109" s="20" t="inlineStr">
+        <is>
+          <t>$5.1M</t>
+        </is>
+      </c>
+      <c r="H109" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="I109" s="20" t="inlineStr">
+        <is>
+          <t>10d</t>
+        </is>
+      </c>
+      <c r="J109" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K109" s="42" t="inlineStr">
+      <c r="K109" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15573,154 +15709,154 @@
     <row r="110" ht="28" customHeight="1">
       <c r="B110" s="17" t="inlineStr">
         <is>
+          <t>GROUP1-24-R-W001</t>
+        </is>
+      </c>
+      <c r="C110" s="33" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>$17.5M</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="J110" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K110" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>36C26126R0050</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+        </is>
+      </c>
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="E111" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>$5.0M</t>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I111" s="23" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="J111" s="23" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K111" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="B112" s="17" t="inlineStr">
+        <is>
           <t>140P8526Q0083</t>
         </is>
       </c>
-      <c r="C110" s="33" t="inlineStr">
+      <c r="C112" s="33" t="inlineStr">
         <is>
           <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E110" s="17" t="inlineStr">
+      <c r="E112" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F110" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="17" t="inlineStr">
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H112" s="17" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="I110" s="17" t="inlineStr">
+      <c r="I112" s="17" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
       </c>
-      <c r="J110" s="17" t="inlineStr">
+      <c r="J112" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K110" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="B111" s="20" t="inlineStr">
-        <is>
-          <t>140P9726Q0046</t>
-        </is>
-      </c>
-      <c r="C111" s="36" t="inlineStr">
-        <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
-        </is>
-      </c>
-      <c r="D111" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E111" s="20" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F111" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G111" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H111" s="20" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I111" s="20" t="inlineStr">
-        <is>
-          <t>12d</t>
-        </is>
-      </c>
-      <c r="J111" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K111" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="B112" s="23" t="inlineStr">
-        <is>
-          <t>36C24726Q0610</t>
-        </is>
-      </c>
-      <c r="C112" s="28" t="inlineStr">
-        <is>
-          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
-        </is>
-      </c>
-      <c r="D112" s="23" t="inlineStr">
-        <is>
-          <t>Columbia, South Carolina</t>
-        </is>
-      </c>
-      <c r="E112" s="23" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F112" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="inlineStr">
-        <is>
-          <t>$47.0M</t>
-        </is>
-      </c>
-      <c r="H112" s="23" t="inlineStr">
-        <is>
-          <t>Jul 01, 2026</t>
-        </is>
-      </c>
-      <c r="I112" s="23" t="inlineStr">
-        <is>
-          <t>18d</t>
-        </is>
-      </c>
-      <c r="J112" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K112" s="42" t="inlineStr">
+      <c r="K112" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15729,12 +15865,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+          <t>140P9726Q0046</t>
         </is>
       </c>
       <c r="C113" s="36" t="inlineStr">
         <is>
-          <t>Repair Hush House Concrete B3857</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -15744,7 +15880,7 @@
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15754,17 +15890,17 @@
       </c>
       <c r="G113" s="20" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
@@ -15779,52 +15915,52 @@
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>693C73-26-R-000047</t>
-        </is>
-      </c>
-      <c r="C114" s="33" t="inlineStr">
-        <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
-        </is>
-      </c>
-      <c r="D114" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E114" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F114" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>$12.9M</t>
-        </is>
-      </c>
-      <c r="H114" s="17" t="inlineStr">
-        <is>
-          <t>Jul 07, 2026</t>
-        </is>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>24d</t>
-        </is>
-      </c>
-      <c r="J114" s="17" t="inlineStr">
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>36C24726Q0610</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
+        </is>
+      </c>
+      <c r="D114" s="23" t="inlineStr">
+        <is>
+          <t>Columbia, South Carolina</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="H114" s="23" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="I114" s="23" t="inlineStr">
+        <is>
+          <t>18d</t>
+        </is>
+      </c>
+      <c r="J114" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K114" s="35" t="inlineStr">
+      <c r="K114" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15833,17 +15969,17 @@
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>W9128F26BA019</t>
+          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
         </is>
       </c>
       <c r="C115" s="36" t="inlineStr">
         <is>
-          <t>Oahe IDCC Road Maintenance 2026</t>
+          <t>Repair Hush House Concrete B3857</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>Fort Pierre, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -15858,77 +15994,77 @@
       </c>
       <c r="G115" s="20" t="inlineStr">
         <is>
-          <t>$21.5M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="I115" s="20" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="J115" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K115" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>693C73-26-R-000047</t>
+        </is>
+      </c>
+      <c r="C116" s="33" t="inlineStr">
+        <is>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>$12.9M</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
           <t>Jul 07, 2026</t>
         </is>
       </c>
-      <c r="I115" s="20" t="inlineStr">
+      <c r="I116" s="17" t="inlineStr">
         <is>
           <t>24d</t>
         </is>
       </c>
-      <c r="J115" s="20" t="inlineStr">
+      <c r="J116" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K115" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="B116" s="23" t="inlineStr">
-        <is>
-          <t>36C24626R0067</t>
-        </is>
-      </c>
-      <c r="C116" s="28" t="inlineStr">
-        <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
-        </is>
-      </c>
-      <c r="D116" s="23" t="inlineStr">
-        <is>
-          <t>Hampton, Virginia</t>
-        </is>
-      </c>
-      <c r="E116" s="23" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F116" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G116" s="23" t="inlineStr">
-        <is>
-          <t>$7.0M</t>
-        </is>
-      </c>
-      <c r="H116" s="23" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I116" s="23" t="inlineStr">
-        <is>
-          <t>30d</t>
-        </is>
-      </c>
-      <c r="J116" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K116" s="42" t="inlineStr">
+      <c r="K116" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15937,22 +16073,22 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>W9128F26BA019</t>
         </is>
       </c>
       <c r="C117" s="36" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Oahe IDCC Road Maintenance 2026</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Pierre, South Dakota</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -15962,77 +16098,77 @@
       </c>
       <c r="G117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$21.5M</t>
         </is>
       </c>
       <c r="H117" s="20" t="inlineStr">
         <is>
+          <t>Jul 07, 2026</t>
+        </is>
+      </c>
+      <c r="I117" s="20" t="inlineStr">
+        <is>
+          <t>24d</t>
+        </is>
+      </c>
+      <c r="J117" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K117" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>36C24626R0067</t>
+        </is>
+      </c>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+        </is>
+      </c>
+      <c r="D118" s="23" t="inlineStr">
+        <is>
+          <t>Hampton, Virginia</t>
+        </is>
+      </c>
+      <c r="E118" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>$7.0M</t>
+        </is>
+      </c>
+      <c r="H118" s="23" t="inlineStr">
+        <is>
           <t>Jul 13, 2026</t>
         </is>
       </c>
-      <c r="I117" s="20" t="inlineStr">
+      <c r="I118" s="23" t="inlineStr">
         <is>
           <t>30d</t>
         </is>
       </c>
-      <c r="J117" s="20" t="inlineStr">
+      <c r="J118" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K117" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="B118" s="17" t="inlineStr">
-        <is>
-          <t>140L2626Q0032</t>
-        </is>
-      </c>
-      <c r="C118" s="33" t="inlineStr">
-        <is>
-          <t>Y--Indian Springs Vault Toilet</t>
-        </is>
-      </c>
-      <c r="D118" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E118" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F118" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G118" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H118" s="17" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I118" s="17" t="inlineStr">
-        <is>
-          <t>30d</t>
-        </is>
-      </c>
-      <c r="J118" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K118" s="35" t="inlineStr">
+      <c r="K118" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16041,12 +16177,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C119" s="36" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
@@ -16056,7 +16192,7 @@
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -16071,12 +16207,12 @@
       </c>
       <c r="H119" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
@@ -16093,22 +16229,22 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
@@ -16123,12 +16259,12 @@
       </c>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="J120" s="17" t="inlineStr">
@@ -16145,12 +16281,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C121" s="36" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Y--Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -16160,7 +16296,7 @@
       </c>
       <c r="E121" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -16175,12 +16311,12 @@
       </c>
       <c r="H121" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>39d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
@@ -16197,22 +16333,22 @@
     <row r="122" ht="28" customHeight="1">
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
@@ -16227,12 +16363,12 @@
       </c>
       <c r="H122" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
-          <t>39d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="J122" s="17" t="inlineStr">
@@ -16249,12 +16385,12 @@
     <row r="123" ht="28" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C123" s="36" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
@@ -16264,7 +16400,7 @@
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -16279,12 +16415,12 @@
       </c>
       <c r="H123" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>39d</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
@@ -16301,12 +16437,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C124" s="33" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
@@ -16331,12 +16467,12 @@
       </c>
       <c r="H124" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>39d</t>
         </is>
       </c>
       <c r="J124" s="17" t="inlineStr">
@@ -16353,12 +16489,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="B125" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C125" s="36" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -16405,12 +16541,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C126" s="33" t="inlineStr">
         <is>
-          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
@@ -16420,7 +16556,7 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -16430,17 +16566,17 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H126" s="17" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
-          <t>44d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="J126" s="17" t="inlineStr">
@@ -16457,12 +16593,12 @@
     <row r="127" ht="28" customHeight="1">
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C127" s="36" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
@@ -16472,7 +16608,7 @@
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -16482,17 +16618,17 @@
       </c>
       <c r="G127" s="20" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H127" s="20" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I127" s="20" t="inlineStr">
         <is>
-          <t>76d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="J127" s="20" t="inlineStr">
@@ -16509,12 +16645,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="C128" s="33" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -16524,7 +16660,7 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -16534,17 +16670,17 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44d</t>
         </is>
       </c>
       <c r="J128" s="17" t="inlineStr">
@@ -16559,52 +16695,52 @@
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
-      <c r="B129" s="23" t="inlineStr">
-        <is>
-          <t>36C25726B0007</t>
-        </is>
-      </c>
-      <c r="C129" s="28" t="inlineStr">
-        <is>
-          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
-        </is>
-      </c>
-      <c r="D129" s="23" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E129" s="23" t="inlineStr">
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>140L3726R0006</t>
+        </is>
+      </c>
+      <c r="C129" s="36" t="inlineStr">
+        <is>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+        </is>
+      </c>
+      <c r="D129" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E129" s="20" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t>$2.5B</t>
-        </is>
-      </c>
-      <c r="H129" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I129" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="23" t="inlineStr">
+      <c r="F129" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G129" s="20" t="inlineStr">
+        <is>
+          <t>$19.0M</t>
+        </is>
+      </c>
+      <c r="H129" s="20" t="inlineStr">
+        <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="I129" s="20" t="inlineStr">
+        <is>
+          <t>76d</t>
+        </is>
+      </c>
+      <c r="J129" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K129" s="42" t="inlineStr">
+      <c r="K129" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16613,12 +16749,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C130" s="33" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
@@ -16628,7 +16764,7 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -16663,52 +16799,52 @@
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
-      <c r="B131" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26BA013</t>
-        </is>
-      </c>
-      <c r="C131" s="36" t="inlineStr">
-        <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
-        </is>
-      </c>
-      <c r="D131" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E131" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F131" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G131" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H131" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I131" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J131" s="20" t="inlineStr">
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t>36C25726B0007</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+        </is>
+      </c>
+      <c r="D131" s="23" t="inlineStr">
+        <is>
+          <t>Waco, Texas</t>
+        </is>
+      </c>
+      <c r="E131" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="H131" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K131" s="38" t="inlineStr">
+      <c r="K131" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16717,12 +16853,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA119</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C132" s="33" t="inlineStr">
         <is>
-          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
@@ -16732,7 +16868,7 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
@@ -16742,7 +16878,7 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
@@ -16769,17 +16905,17 @@
     <row r="133" ht="28" customHeight="1">
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>W911WN26BA008</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C133" s="36" t="inlineStr">
         <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
         <is>
-          <t>Saltsburg, Pennsylvania</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
@@ -16794,7 +16930,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H133" s="20" t="inlineStr">
@@ -16821,12 +16957,12 @@
     <row r="134" ht="28" customHeight="1">
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W912WJ26QA119</t>
         </is>
       </c>
       <c r="C134" s="33" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D134" s="17" t="inlineStr">
@@ -16836,7 +16972,7 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
@@ -16846,7 +16982,7 @@
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H134" s="17" t="inlineStr">
@@ -16873,22 +17009,22 @@
     <row r="135" ht="28" customHeight="1">
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C135" s="36" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Saltsburg, Pennsylvania</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -16898,7 +17034,7 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H135" s="20" t="inlineStr">
@@ -16925,12 +17061,12 @@
     <row r="136" ht="28" customHeight="1">
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C136" s="33" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D136" s="17" t="inlineStr">
@@ -16940,7 +17076,7 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
@@ -16950,7 +17086,7 @@
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H136" s="17" t="inlineStr">
@@ -16977,102 +17113,102 @@
     <row r="137" ht="28" customHeight="1">
       <c r="B137" s="20" t="inlineStr">
         <is>
-          <t>W9128F26RA107</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="C137" s="36" t="inlineStr">
         <is>
-          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F137" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G137" s="20" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H137" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J137" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K137" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>140FGA26R0028</t>
+        </is>
+      </c>
+      <c r="C138" s="33" t="inlineStr">
+        <is>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E137" s="20" t="inlineStr">
+      <c r="E138" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F137" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G137" s="20" t="inlineStr">
-        <is>
-          <t>$30.0M</t>
-        </is>
-      </c>
-      <c r="H137" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I137" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J137" s="20" t="inlineStr">
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="H138" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K137" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="28" customHeight="1">
-      <c r="B138" s="23" t="inlineStr">
-        <is>
-          <t>36C24226B0057</t>
-        </is>
-      </c>
-      <c r="C138" s="28" t="inlineStr">
-        <is>
-          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
-        </is>
-      </c>
-      <c r="D138" s="23" t="inlineStr">
-        <is>
-          <t>Buffalo, New York</t>
-        </is>
-      </c>
-      <c r="E138" s="23" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="F138" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G138" s="23" t="inlineStr">
-        <is>
-          <t>$16.2M</t>
-        </is>
-      </c>
-      <c r="H138" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I138" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J138" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K138" s="42" t="inlineStr">
+      <c r="K138" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -17081,17 +17217,17 @@
     <row r="139" ht="28" customHeight="1">
       <c r="B139" s="20" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>W9128F26RA107</t>
         </is>
       </c>
       <c r="C139" s="36" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -17106,7 +17242,7 @@
       </c>
       <c r="G139" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$30.0M</t>
         </is>
       </c>
       <c r="H139" s="20" t="inlineStr">
@@ -17131,52 +17267,52 @@
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
-      <c r="B140" s="17" t="inlineStr">
-        <is>
-          <t>12445526Q0069</t>
-        </is>
-      </c>
-      <c r="C140" s="33" t="inlineStr">
-        <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
-        </is>
-      </c>
-      <c r="D140" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E140" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F140" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G140" s="17" t="inlineStr">
-        <is>
-          <t>$25K</t>
-        </is>
-      </c>
-      <c r="H140" s="17" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>11d</t>
-        </is>
-      </c>
-      <c r="J140" s="17" t="inlineStr">
-        <is>
-          <t>Special Notice</t>
-        </is>
-      </c>
-      <c r="K140" s="35" t="inlineStr">
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>36C24226B0057</t>
+        </is>
+      </c>
+      <c r="C140" s="28" t="inlineStr">
+        <is>
+          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
+        </is>
+      </c>
+      <c r="D140" s="23" t="inlineStr">
+        <is>
+          <t>Buffalo, New York</t>
+        </is>
+      </c>
+      <c r="E140" s="23" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="F140" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G140" s="23" t="inlineStr">
+        <is>
+          <t>$16.2M</t>
+        </is>
+      </c>
+      <c r="H140" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="23" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K140" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -17185,22 +17321,22 @@
     <row r="141" ht="28" customHeight="1">
       <c r="B141" s="20" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C141" s="36" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E141" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -17215,17 +17351,17 @@
       </c>
       <c r="H141" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I141" s="20" t="inlineStr">
         <is>
-          <t>17d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J141" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K141" s="38" t="inlineStr">
@@ -17237,57 +17373,161 @@
     <row r="142" ht="28" customHeight="1">
       <c r="B142" s="17" t="inlineStr">
         <is>
+          <t>12445526Q0069</t>
+        </is>
+      </c>
+      <c r="C142" s="33" t="inlineStr">
+        <is>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="J142" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K142" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>SP470525R002026</t>
+        </is>
+      </c>
+      <c r="C143" s="36" t="inlineStr">
+        <is>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+        </is>
+      </c>
+      <c r="D143" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E143" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F143" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G143" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="20" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I143" s="20" t="inlineStr">
+        <is>
+          <t>17d</t>
+        </is>
+      </c>
+      <c r="J143" s="20" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K143" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="B144" s="17" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C142" s="33" t="inlineStr">
+      <c r="C144" s="33" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E142" s="17" t="inlineStr">
+      <c r="E144" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F142" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J142" s="17" t="inlineStr">
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="17" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K142" s="35" t="inlineStr">
+      <c r="K144" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K142"/>
+  <autoFilter ref="B5:K144"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -17430,6 +17670,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17442,7 +17684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K76"/>
+  <dimension ref="B2:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -17470,7 +17712,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="47" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  71 records  (14 SDVOSB)  ·  June 12, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  73 records  (15 SDVOSB)  ·  June 12, 2026</t>
         </is>
       </c>
     </row>
@@ -17790,17 +18032,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="B11" s="49" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C11" s="50" t="inlineStr">
         <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>Fayetteville, Arkansas</t>
+          <t>Madison, Wisconsin</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
@@ -17810,17 +18052,17 @@
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
-          <t>$15.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="51" t="inlineStr">
         <is>
-          <t>Jul 23, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H11" s="51" t="inlineStr">
         <is>
-          <t>40d</t>
+          <t>17d</t>
         </is>
       </c>
       <c r="I11" s="51" t="inlineStr">
@@ -17828,9 +18070,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J11" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K11" s="53" t="inlineStr">
@@ -17842,17 +18084,17 @@
     <row r="12" ht="28" customHeight="1">
       <c r="B12" s="49" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C12" s="50" t="inlineStr">
         <is>
-          <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
         </is>
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>Orlando, Florida</t>
+          <t>Fayetteville, Arkansas</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
@@ -17862,27 +18104,27 @@
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$15.0M</t>
         </is>
       </c>
       <c r="G12" s="51" t="inlineStr">
         <is>
-          <t>Jun 15, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="H12" s="51" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>40d</t>
         </is>
       </c>
       <c r="I12" s="51" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K12" s="53" t="inlineStr">
@@ -17899,12 +18141,12 @@
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
+          <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Orlando, Florida</t>
         </is>
       </c>
       <c r="E13" s="52" t="inlineStr">
@@ -17919,12 +18161,12 @@
       </c>
       <c r="G13" s="51" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 15, 2026</t>
         </is>
       </c>
       <c r="H13" s="51" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="I13" s="51" t="inlineStr">
@@ -17946,17 +18188,17 @@
     <row r="14" ht="28" customHeight="1">
       <c r="B14" s="49" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C14" s="50" t="inlineStr">
         <is>
-          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
+          <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
         </is>
       </c>
       <c r="D14" s="51" t="inlineStr">
         <is>
-          <t>Dayton, Ohio</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E14" s="52" t="inlineStr">
@@ -17966,17 +18208,17 @@
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="51" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 17, 2026</t>
         </is>
       </c>
       <c r="H14" s="51" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="I14" s="51" t="inlineStr">
@@ -17998,17 +18240,17 @@
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="49" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C15" s="50" t="inlineStr">
         <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>Reno, NV</t>
+          <t>Dayton, Ohio</t>
         </is>
       </c>
       <c r="E15" s="52" t="inlineStr">
@@ -18018,17 +18260,17 @@
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
-          <t>$5.0M</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="G15" s="51" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H15" s="51" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="I15" s="51" t="inlineStr">
@@ -18050,17 +18292,17 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="49" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C16" s="50" t="inlineStr">
         <is>
-          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>Columbia, South Carolina</t>
+          <t>Reno, NV</t>
         </is>
       </c>
       <c r="E16" s="52" t="inlineStr">
@@ -18070,17 +18312,17 @@
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>$5.0M</t>
         </is>
       </c>
       <c r="G16" s="51" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="H16" s="51" t="inlineStr">
         <is>
-          <t>18d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="I16" s="51" t="inlineStr">
@@ -18088,9 +18330,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J16" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K16" s="53" t="inlineStr">
@@ -18102,17 +18344,17 @@
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="49" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C17" s="50" t="inlineStr">
         <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>Hampton, Virginia</t>
+          <t>Columbia, South Carolina</t>
         </is>
       </c>
       <c r="E17" s="52" t="inlineStr">
@@ -18122,17 +18364,17 @@
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
-          <t>$7.0M</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G17" s="51" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 01, 2026</t>
         </is>
       </c>
       <c r="H17" s="51" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>18d</t>
         </is>
       </c>
       <c r="I17" s="51" t="inlineStr">
@@ -18159,12 +18401,12 @@
       </c>
       <c r="C18" s="50" t="inlineStr">
         <is>
-          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
         </is>
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Hampton, Virginia</t>
         </is>
       </c>
       <c r="E18" s="52" t="inlineStr">
@@ -18174,17 +18416,17 @@
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
-          <t>$2.5B</t>
+          <t>$7.0M</t>
         </is>
       </c>
       <c r="G18" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="H18" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="I18" s="51" t="inlineStr">
@@ -18192,9 +18434,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J18" s="44" t="inlineStr">
-        <is>
-          <t>Pre-Sol</t>
+      <c r="J18" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K18" s="53" t="inlineStr">
@@ -18206,102 +18448,102 @@
     <row r="19" ht="28" customHeight="1">
       <c r="B19" s="49" t="inlineStr">
         <is>
+          <t>238210 — Electrical Contractors</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>Waco, Texas</t>
+        </is>
+      </c>
+      <c r="E19" s="52" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="51" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K19" s="53" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="49" t="inlineStr">
+        <is>
           <t>237120 — Oil &amp; Gas Pipeline</t>
         </is>
       </c>
-      <c r="C19" s="50" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
         </is>
       </c>
-      <c r="D19" s="51" t="inlineStr">
+      <c r="D20" s="51" t="inlineStr">
         <is>
           <t>Buffalo, New York</t>
         </is>
       </c>
-      <c r="E19" s="52" t="inlineStr">
+      <c r="E20" s="52" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="F19" s="51" t="inlineStr">
+      <c r="F20" s="51" t="inlineStr">
         <is>
           <t>$16.2M</t>
         </is>
       </c>
-      <c r="G19" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" s="51" t="inlineStr">
+      <c r="G20" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="51" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J19" s="44" t="inlineStr">
+      <c r="J20" s="44" t="inlineStr">
         <is>
           <t>Pre-Sol</t>
         </is>
       </c>
-      <c r="K19" s="53" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>237110 — Water &amp; Sewer</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>CA-FWS MODOC NWR-WATER MAIN REPAIR</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>$58K</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>Jun 15, 2026</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
-        </is>
-      </c>
-      <c r="K20" s="35" t="inlineStr">
+      <c r="K20" s="53" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -18310,12 +18552,12 @@
     <row r="21" ht="28" customHeight="1">
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C21" s="55" t="inlineStr">
         <is>
-          <t>Z--Verona-Great Falls 161KV Transmission Line Rebuild</t>
+          <t>CA-FWS MODOC NWR-WATER MAIN REPAIR</t>
         </is>
       </c>
       <c r="D21" s="56" t="inlineStr">
@@ -18330,7 +18572,7 @@
       </c>
       <c r="F21" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$58K</t>
         </is>
       </c>
       <c r="G21" s="56" t="inlineStr">
@@ -18362,17 +18604,17 @@
     <row r="22" ht="28" customHeight="1">
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable B230 to B9511</t>
+          <t>Z--Verona-Great Falls 161KV Transmission Line Rebuild</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
@@ -18387,12 +18629,12 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jun 15, 2026</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
@@ -18414,17 +18656,17 @@
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>237120 — Oil &amp; Gas Pipeline</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C23" s="55" t="inlineStr">
         <is>
-          <t>Replace Fuel Tanks and Associated Lines - Rec Camp</t>
+          <t>Fiber Optic Cable B230 to B9511</t>
         </is>
       </c>
       <c r="D23" s="56" t="inlineStr">
         <is>
-          <t>San Angelo, Texas</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="E23" s="56" t="inlineStr">
@@ -18439,12 +18681,12 @@
       </c>
       <c r="G23" s="56" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="H23" s="56" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="I23" s="56" t="inlineStr">
@@ -18466,17 +18708,17 @@
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237120 — Oil &amp; Gas Pipeline</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
+          <t>Replace Fuel Tanks and Associated Lines - Rec Camp</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>San Angelo, Texas</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -18491,12 +18733,12 @@
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 17, 2026</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
@@ -18523,12 +18765,12 @@
       </c>
       <c r="C25" s="55" t="inlineStr">
         <is>
-          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
+          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
         </is>
       </c>
       <c r="D25" s="56" t="inlineStr">
         <is>
-          <t>Paicines</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E25" s="56" t="inlineStr">
@@ -18543,12 +18785,12 @@
       </c>
       <c r="G25" s="56" t="inlineStr">
         <is>
-          <t>Jun 19, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H25" s="56" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="I25" s="56" t="inlineStr">
@@ -18570,17 +18812,17 @@
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESGIN BUILD/DESIGN BID BUILD ENVIRONMENTAL INFRASTRUCTURE MATOC  </t>
+          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Paicines</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
@@ -18590,17 +18832,17 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>$6.6M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 19, 2026</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
@@ -18627,7 +18869,7 @@
       </c>
       <c r="C27" s="55" t="inlineStr">
         <is>
-          <t>Y--PAIS WASTE WATER TANK REPLACEMENT</t>
+          <t xml:space="preserve">DESGIN BUILD/DESIGN BID BUILD ENVIRONMENTAL INFRASTRUCTURE MATOC  </t>
         </is>
       </c>
       <c r="D27" s="56" t="inlineStr">
@@ -18642,7 +18884,7 @@
       </c>
       <c r="F27" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$6.6M</t>
         </is>
       </c>
       <c r="G27" s="56" t="inlineStr">
@@ -18674,17 +18916,17 @@
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>Repair Kiddie Pool</t>
+          <t>Y--PAIS WASTE WATER TANK REPLACEMENT</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Columbus, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -18694,7 +18936,7 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -18726,17 +18968,17 @@
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
+          <t>Repair Kiddie Pool</t>
         </is>
       </c>
       <c r="D29" s="56" t="inlineStr">
         <is>
-          <t>Stanton, North Dakota</t>
+          <t>Columbus, Mississippi</t>
         </is>
       </c>
       <c r="E29" s="56" t="inlineStr">
@@ -18746,17 +18988,17 @@
       </c>
       <c r="F29" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="G29" s="56" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H29" s="56" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="I29" s="56" t="inlineStr">
@@ -18778,17 +19020,17 @@
     <row r="30" ht="28" customHeight="1">
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>23 STS HPTC Surround Sound Installation</t>
+          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Hurlburt Field, Florida</t>
+          <t>Stanton, North Dakota</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
@@ -18830,17 +19072,17 @@
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C31" s="55" t="inlineStr">
         <is>
-          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
+          <t>23 STS HPTC Surround Sound Installation</t>
         </is>
       </c>
       <c r="D31" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Hurlburt Field, Florida</t>
         </is>
       </c>
       <c r="E31" s="56" t="inlineStr">
@@ -18882,12 +19124,12 @@
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -18939,7 +19181,7 @@
       </c>
       <c r="C33" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="D33" s="56" t="inlineStr">
@@ -18986,12 +19228,12 @@
     <row r="34" ht="28" customHeight="1">
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
+          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -19043,7 +19285,7 @@
       </c>
       <c r="C35" s="55" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
         </is>
       </c>
       <c r="D35" s="56" t="inlineStr">
@@ -19063,12 +19305,12 @@
       </c>
       <c r="G35" s="56" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H35" s="56" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="I35" s="56" t="inlineStr">
@@ -19090,12 +19332,12 @@
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>213112 — Support Activities Oil &amp; Gas</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
+          <t>Y--GLBA REHAB WATERLINE</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
@@ -19142,12 +19384,12 @@
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>213112 — Support Activities Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C37" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Base Operations Support (BOS) Services at Naval Air Station (NAS) Whiting Field and Outlying Areas</t>
+          <t>EO14398 UST ASSESSMENT &amp; REPORTING - GLBA</t>
         </is>
       </c>
       <c r="D37" s="56" t="inlineStr">
@@ -19167,12 +19409,12 @@
       </c>
       <c r="G37" s="56" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="H37" s="56" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="I37" s="56" t="inlineStr">
@@ -19194,12 +19436,12 @@
     <row r="38" ht="28" customHeight="1">
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t xml:space="preserve"> Base Operations Support (BOS) Services at Naval Air Station (NAS) Whiting Field and Outlying Areas</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -19214,7 +19456,7 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -19251,12 +19493,12 @@
       </c>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="D39" s="56" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E39" s="56" t="inlineStr">
@@ -19266,7 +19508,7 @@
       </c>
       <c r="F39" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="G39" s="56" t="inlineStr">
@@ -20442,17 +20684,17 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -20467,12 +20709,12 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -20480,9 +20722,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J62" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J62" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K62" s="35" t="inlineStr">
@@ -20494,17 +20736,17 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D63" s="56" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E63" s="56" t="inlineStr">
@@ -20514,27 +20756,27 @@
       </c>
       <c r="F63" s="56" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G63" s="56" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H63" s="56" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="I63" s="56" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="J63" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="J63" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K63" s="57" t="inlineStr">
@@ -20546,12 +20788,12 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Water Tank Storage</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -20571,22 +20813,22 @@
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>33d</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="J64" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="J64" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K64" s="35" t="inlineStr">
@@ -20598,17 +20840,17 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D65" s="56" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E65" s="56" t="inlineStr">
@@ -20618,17 +20860,17 @@
       </c>
       <c r="F65" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="G65" s="56" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H65" s="56" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="I65" s="56" t="inlineStr">
@@ -20650,17 +20892,17 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -20670,7 +20912,7 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -20702,17 +20944,17 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D67" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E67" s="56" t="inlineStr">
@@ -20722,17 +20964,17 @@
       </c>
       <c r="F67" s="56" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="56" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H67" s="56" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="I67" s="56" t="inlineStr">
@@ -20754,17 +20996,17 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -20774,17 +21016,17 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -20806,12 +21048,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="54" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D69" s="56" t="inlineStr">
@@ -20826,17 +21068,17 @@
       </c>
       <c r="F69" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="G69" s="56" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H69" s="56" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="I69" s="56" t="inlineStr">
@@ -20844,9 +21086,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J69" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K69" s="57" t="inlineStr">
@@ -20858,17 +21100,17 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -20883,12 +21125,12 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -20896,9 +21138,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J70" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J70" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K70" s="35" t="inlineStr">
@@ -20910,12 +21152,12 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C71" s="55" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D71" s="56" t="inlineStr">
@@ -20935,12 +21177,12 @@
       </c>
       <c r="G71" s="56" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H71" s="56" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="I71" s="56" t="inlineStr">
@@ -20962,17 +21204,17 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -20987,12 +21229,12 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
@@ -21014,12 +21256,12 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C73" s="55" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D73" s="56" t="inlineStr">
@@ -21034,17 +21276,17 @@
       </c>
       <c r="F73" s="56" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="56" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H73" s="56" t="inlineStr">
         <is>
-          <t>76d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="I73" s="56" t="inlineStr">
@@ -21071,7 +21313,7 @@
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
@@ -21091,12 +21333,12 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
@@ -21106,7 +21348,7 @@
       </c>
       <c r="J74" s="44" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K74" s="35" t="inlineStr">
@@ -21118,17 +21360,17 @@
     <row r="75" ht="28" customHeight="1">
       <c r="B75" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C75" s="55" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D75" s="56" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E75" s="56" t="inlineStr">
@@ -21138,17 +21380,17 @@
       </c>
       <c r="F75" s="56" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G75" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H75" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76d</t>
         </is>
       </c>
       <c r="I75" s="56" t="inlineStr">
@@ -21158,7 +21400,7 @@
       </c>
       <c r="J75" s="44" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K75" s="57" t="inlineStr">
@@ -21170,57 +21412,161 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="16" t="inlineStr">
         <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J76" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K76" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="B77" s="54" t="inlineStr">
+        <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C77" s="55" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D77" s="56" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E77" s="56" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F77" s="56" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="G77" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="56" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J77" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K77" s="57" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="B78" s="16" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C76" s="33" t="inlineStr">
+      <c r="C78" s="33" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="17" t="inlineStr">
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H76" s="17" t="inlineStr">
+      <c r="H78" s="17" t="inlineStr">
         <is>
           <t>17d</t>
         </is>
       </c>
-      <c r="I76" s="17" t="inlineStr">
+      <c r="I78" s="17" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J76" s="43" t="inlineStr">
+      <c r="J78" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="K76" s="35" t="inlineStr">
+      <c r="K78" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K76"/>
+  <autoFilter ref="B5:K78"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -21297,6 +21643,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
